--- a/artfynd/A 10362-2026 artfynd.xlsx
+++ b/artfynd/A 10362-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8505,6 +8505,862 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131935849</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>516643</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7204401</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131935843</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>516717</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7204264</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131935846</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92562</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>516689</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7204338</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131935848</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>516672</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7204386</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131935844</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>516715</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7204172</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131935847</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>516689</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7204340</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131935850</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>516622</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7204393</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131935845</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79267</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kökarbacken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>516714</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7204237</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10362-2026 artfynd.xlsx
+++ b/artfynd/A 10362-2026 artfynd.xlsx
@@ -8510,7 +8510,7 @@
         <v>131935849</v>
       </c>
       <c r="B71" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>131935843</v>
       </c>
       <c r="B72" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>131935846</v>
       </c>
       <c r="B73" t="n">
-        <v>92562</v>
+        <v>92564</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>131935848</v>
       </c>
       <c r="B74" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131935844</v>
+        <v>131935847</v>
       </c>
       <c r="B75" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>516715</v>
+        <v>516689</v>
       </c>
       <c r="R75" t="n">
-        <v>7204172</v>
+        <v>7204340</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9042,10 +9042,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131935847</v>
+        <v>131935844</v>
       </c>
       <c r="B76" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>516689</v>
+        <v>516715</v>
       </c>
       <c r="R76" t="n">
-        <v>7204340</v>
+        <v>7204172</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9152,7 +9152,7 @@
         <v>131935850</v>
       </c>
       <c r="B77" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>131935845</v>
       </c>
       <c r="B78" t="n">
-        <v>79267</v>
+        <v>79269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 10362-2026 artfynd.xlsx
+++ b/artfynd/A 10362-2026 artfynd.xlsx
@@ -8510,7 +8510,7 @@
         <v>131935849</v>
       </c>
       <c r="B71" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>131935843</v>
       </c>
       <c r="B72" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>131935846</v>
       </c>
       <c r="B73" t="n">
-        <v>92564</v>
+        <v>92569</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>131935848</v>
       </c>
       <c r="B74" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>131935847</v>
       </c>
       <c r="B75" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>131935844</v>
       </c>
       <c r="B76" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>131935850</v>
       </c>
       <c r="B77" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>131935845</v>
       </c>
       <c r="B78" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 10362-2026 artfynd.xlsx
+++ b/artfynd/A 10362-2026 artfynd.xlsx
@@ -8510,7 +8510,7 @@
         <v>131935849</v>
       </c>
       <c r="B71" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>131935843</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>131935846</v>
       </c>
       <c r="B73" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>131935848</v>
       </c>
       <c r="B74" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>131935847</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>131935844</v>
       </c>
       <c r="B76" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>131935850</v>
       </c>
       <c r="B77" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>131935845</v>
       </c>
       <c r="B78" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
